--- a/DateBase/orders/Nhat 48_2026-9-22.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-22.xlsx
@@ -1167,6 +1167,9 @@
       <c r="G2" t="str">
         <v>010103015555151510205510101015510103010109865310781571027291071505105105101010105105515105141030102010101055555555209123524</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
